--- a/north_arlington.xlsx
+++ b/north_arlington.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C10E7CE-F8C4-4544-A97B-41539FDD56E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF376952-264D-40FC-B34D-CB3088B7219F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2530" yWindow="2580" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Carrier Route Scheme" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3288" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3279" uniqueCount="575">
   <si>
     <t>Scheme Listing by CRID for ZIP Code 07031</t>
   </si>
@@ -1733,7 +1733,7 @@
     <t>60</t>
   </si>
   <si>
-    <t>Total Line items: 364</t>
+    <t>Total Line items: 363</t>
   </si>
   <si>
     <t>zip code</t>
@@ -1746,7 +1746,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1758,6 +1758,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2141,7 +2148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I367"/>
+  <dimension ref="A1:I366"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="8" customWidth="1"/>
@@ -10104,13 +10111,13 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A276" s="3" t="s">
-        <v>351</v>
+        <v>446</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>351</v>
+        <v>447</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D276" t="s">
         <v>8</v>
@@ -10128,18 +10135,18 @@
         <v>574</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A277" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D277" t="s">
         <v>8</v>
@@ -10157,15 +10164,15 @@
         <v>574</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A278" s="3" t="s">
-        <v>448</v>
+        <v>385</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>23</v>
@@ -10186,15 +10193,15 @@
         <v>574</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A279" s="3" t="s">
-        <v>385</v>
+        <v>450</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>23</v>
@@ -10215,15 +10222,15 @@
         <v>574</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A280" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>23</v>
@@ -10249,10 +10256,10 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A281" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>23</v>
@@ -10278,10 +10285,10 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A282" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>23</v>
@@ -10307,10 +10314,10 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A283" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>23</v>
@@ -10336,10 +10343,10 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A284" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>23</v>
@@ -10365,10 +10372,10 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A285" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>23</v>
@@ -10394,10 +10401,10 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A286" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>23</v>
@@ -10423,10 +10430,10 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A287" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>23</v>
@@ -10452,10 +10459,10 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A288" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>23</v>
@@ -10481,10 +10488,10 @@
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A289" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>23</v>
@@ -10510,10 +10517,10 @@
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A290" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>23</v>
@@ -10539,10 +10546,10 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A291" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>23</v>
@@ -10568,10 +10575,10 @@
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A292" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>23</v>
@@ -10597,10 +10604,10 @@
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A293" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>23</v>
@@ -10626,10 +10633,10 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A294" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>23</v>
@@ -10655,10 +10662,10 @@
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A295" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>23</v>
@@ -10684,10 +10691,10 @@
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A296" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>23</v>
@@ -10713,10 +10720,10 @@
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A297" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>23</v>
@@ -10742,10 +10749,10 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A298" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>23</v>
@@ -10771,10 +10778,10 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A299" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>23</v>
@@ -10800,10 +10807,10 @@
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A300" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>23</v>
@@ -10829,10 +10836,10 @@
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A301" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>23</v>
@@ -10858,10 +10865,10 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A302" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>23</v>
@@ -10887,13 +10894,13 @@
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A303" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>494</v>
+        <v>398</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D303" t="s">
         <v>8</v>
@@ -10916,13 +10923,13 @@
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A304" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>398</v>
+        <v>496</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D304" t="s">
         <v>8</v>
@@ -10945,10 +10952,10 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A305" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>23</v>
@@ -10969,18 +10976,18 @@
         <v>574</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A306" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D306" t="s">
         <v>8</v>
@@ -11003,13 +11010,13 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A307" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D307" t="s">
         <v>8</v>
@@ -11027,15 +11034,15 @@
         <v>574</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A308" s="3" t="s">
-        <v>501</v>
+        <v>5</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>502</v>
+        <v>6</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>7</v>
@@ -11044,10 +11051,10 @@
         <v>8</v>
       </c>
       <c r="E308" t="s">
-        <v>439</v>
+        <v>503</v>
       </c>
       <c r="F308" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="G308" t="s">
         <v>8</v>
@@ -11056,7 +11063,7 @@
         <v>574</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.35">
@@ -11064,19 +11071,19 @@
         <v>5</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>6</v>
+        <v>504</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D309" t="s">
         <v>8</v>
       </c>
       <c r="E309" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F309" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="G309" t="s">
         <v>8</v>
@@ -11085,18 +11092,18 @@
         <v>574</v>
       </c>
       <c r="I309" s="1" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A310" s="3" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D310" t="s">
         <v>8</v>
@@ -11119,13 +11126,13 @@
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A311" s="3" t="s">
-        <v>28</v>
+        <v>507</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D311" t="s">
         <v>8</v>
@@ -11148,10 +11155,10 @@
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A312" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>23</v>
@@ -11177,13 +11184,13 @@
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A313" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D313" t="s">
         <v>8</v>
@@ -11206,13 +11213,13 @@
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A314" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D314" t="s">
         <v>8</v>
@@ -11230,18 +11237,18 @@
         <v>574</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A315" s="3" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>511</v>
+        <v>80</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D315" t="s">
         <v>8</v>
@@ -11264,13 +11271,13 @@
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A316" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>80</v>
+        <v>514</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D316" t="s">
         <v>8</v>
@@ -11293,13 +11300,13 @@
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A317" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D317" t="s">
         <v>8</v>
@@ -11317,15 +11324,15 @@
         <v>574</v>
       </c>
       <c r="I317" s="1" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A318" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>516</v>
+        <v>399</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>7</v>
@@ -11346,27 +11353,27 @@
         <v>574</v>
       </c>
       <c r="I318" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A319" s="3" t="s">
-        <v>517</v>
+        <v>5</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>399</v>
+        <v>518</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D319" t="s">
         <v>8</v>
       </c>
       <c r="E319" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="F319" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="G319" t="s">
         <v>8</v>
@@ -11375,18 +11382,18 @@
         <v>574</v>
       </c>
       <c r="I319" s="1" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A320" s="3" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>518</v>
+        <v>128</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D320" t="s">
         <v>8</v>
@@ -11409,10 +11416,10 @@
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A321" s="3" t="s">
-        <v>28</v>
+        <v>520</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>128</v>
+        <v>521</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>20</v>
@@ -11433,18 +11440,18 @@
         <v>574</v>
       </c>
       <c r="I321" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A322" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D322" t="s">
         <v>8</v>
@@ -11467,13 +11474,13 @@
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A323" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D323" t="s">
         <v>8</v>
@@ -11491,15 +11498,15 @@
         <v>574</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A324" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>525</v>
+        <v>388</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>7</v>
@@ -11520,15 +11527,15 @@
         <v>574</v>
       </c>
       <c r="I324" s="1" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A325" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>388</v>
+        <v>528</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>7</v>
@@ -11549,15 +11556,15 @@
         <v>574</v>
       </c>
       <c r="I325" s="1" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A326" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>7</v>
@@ -11578,15 +11585,15 @@
         <v>574</v>
       </c>
       <c r="I326" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A327" s="3" t="s">
-        <v>529</v>
+        <v>5</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>530</v>
+        <v>6</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>7</v>
@@ -11595,10 +11602,10 @@
         <v>8</v>
       </c>
       <c r="E327" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="F327" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="G327" t="s">
         <v>8</v>
@@ -11607,7 +11614,7 @@
         <v>574</v>
       </c>
       <c r="I327" s="1" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.35">
@@ -11615,19 +11622,19 @@
         <v>5</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>6</v>
+        <v>241</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D328" t="s">
         <v>8</v>
       </c>
       <c r="E328" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F328" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="G328" t="s">
         <v>8</v>
@@ -11636,18 +11643,18 @@
         <v>574</v>
       </c>
       <c r="I328" s="1" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A329" s="3" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>241</v>
+        <v>533</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D329" t="s">
         <v>8</v>
@@ -11670,13 +11677,13 @@
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A330" s="3" t="s">
-        <v>28</v>
+        <v>534</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D330" t="s">
         <v>8</v>
@@ -11699,10 +11706,10 @@
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A331" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>23</v>
@@ -11723,18 +11730,18 @@
         <v>574</v>
       </c>
       <c r="I331" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A332" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>536</v>
+        <v>93</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D332" t="s">
         <v>8</v>
@@ -11757,13 +11764,13 @@
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A333" s="3" t="s">
-        <v>537</v>
+        <v>94</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D333" t="s">
         <v>8</v>
@@ -11781,15 +11788,15 @@
         <v>574</v>
       </c>
       <c r="I333" s="1" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A334" s="3" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>65</v>
+        <v>398</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>7</v>
@@ -11798,10 +11805,10 @@
         <v>8</v>
       </c>
       <c r="E334" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="F334" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="G334" t="s">
         <v>8</v>
@@ -11810,15 +11817,15 @@
         <v>574</v>
       </c>
       <c r="I334" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A335" s="3" t="s">
-        <v>5</v>
+        <v>539</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>398</v>
+        <v>539</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>7</v>
@@ -11844,13 +11851,13 @@
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A336" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D336" t="s">
         <v>8</v>
@@ -11868,18 +11875,18 @@
         <v>574</v>
       </c>
       <c r="I336" s="1" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A337" s="3" t="s">
-        <v>540</v>
+        <v>499</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D337" t="s">
         <v>8</v>
@@ -11897,18 +11904,18 @@
         <v>574</v>
       </c>
       <c r="I337" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A338" s="3" t="s">
-        <v>499</v>
+        <v>543</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D338" t="s">
         <v>8</v>
@@ -11931,10 +11938,10 @@
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A339" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>23</v>
@@ -11955,15 +11962,15 @@
         <v>574</v>
       </c>
       <c r="I339" s="1" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A340" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>23</v>
@@ -11984,15 +11991,15 @@
         <v>574</v>
       </c>
       <c r="I340" s="1" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A341" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>548</v>
+        <v>498</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>23</v>
@@ -12013,18 +12020,18 @@
         <v>574</v>
       </c>
       <c r="I341" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A342" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D342" t="s">
         <v>8</v>
@@ -12042,24 +12049,24 @@
         <v>574</v>
       </c>
       <c r="I342" s="1" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A343" s="3" t="s">
-        <v>550</v>
+        <v>5</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D343" t="s">
         <v>8</v>
       </c>
       <c r="E343" t="s">
-        <v>538</v>
+        <v>551</v>
       </c>
       <c r="F343" t="s">
         <v>58</v>
@@ -12071,7 +12078,7 @@
         <v>574</v>
       </c>
       <c r="I343" s="1" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.35">
@@ -12088,10 +12095,10 @@
         <v>8</v>
       </c>
       <c r="E344" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F344" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G344" t="s">
         <v>8</v>
@@ -12100,7 +12107,7 @@
         <v>574</v>
       </c>
       <c r="I344" s="1" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.35">
@@ -12117,7 +12124,7 @@
         <v>8</v>
       </c>
       <c r="E345" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F345" t="s">
         <v>47</v>
@@ -12129,7 +12136,7 @@
         <v>574</v>
       </c>
       <c r="I345" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.35">
@@ -12137,7 +12144,7 @@
         <v>5</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>7</v>
@@ -12146,7 +12153,7 @@
         <v>8</v>
       </c>
       <c r="E346" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F346" t="s">
         <v>47</v>
@@ -12158,7 +12165,7 @@
         <v>574</v>
       </c>
       <c r="I346" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.35">
@@ -12166,7 +12173,7 @@
         <v>5</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>7</v>
@@ -12175,10 +12182,10 @@
         <v>8</v>
       </c>
       <c r="E347" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F347" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="G347" t="s">
         <v>8</v>
@@ -12187,7 +12194,7 @@
         <v>574</v>
       </c>
       <c r="I347" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.35">
@@ -12195,7 +12202,7 @@
         <v>5</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>7</v>
@@ -12204,10 +12211,10 @@
         <v>8</v>
       </c>
       <c r="E348" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F348" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G348" t="s">
         <v>8</v>
@@ -12216,7 +12223,7 @@
         <v>574</v>
       </c>
       <c r="I348" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.35">
@@ -12224,7 +12231,7 @@
         <v>5</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>7</v>
@@ -12233,10 +12240,10 @@
         <v>8</v>
       </c>
       <c r="E349" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F349" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="G349" t="s">
         <v>8</v>
@@ -12245,7 +12252,7 @@
         <v>574</v>
       </c>
       <c r="I349" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.35">
@@ -12253,7 +12260,7 @@
         <v>5</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>7</v>
@@ -12262,10 +12269,10 @@
         <v>8</v>
       </c>
       <c r="E350" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F350" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="G350" t="s">
         <v>8</v>
@@ -12274,7 +12281,7 @@
         <v>574</v>
       </c>
       <c r="I350" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.35">
@@ -12282,7 +12289,7 @@
         <v>5</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>6</v>
+        <v>133</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>7</v>
@@ -12291,10 +12298,10 @@
         <v>8</v>
       </c>
       <c r="E351" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F351" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="G351" t="s">
         <v>8</v>
@@ -12303,15 +12310,15 @@
         <v>574</v>
       </c>
       <c r="I351" s="1" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A352" s="3" t="s">
-        <v>5</v>
+        <v>135</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>133</v>
+        <v>65</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>7</v>
@@ -12332,15 +12339,15 @@
         <v>574</v>
       </c>
       <c r="I352" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A353" s="3" t="s">
-        <v>135</v>
+        <v>5</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>7</v>
@@ -12352,7 +12359,7 @@
         <v>559</v>
       </c>
       <c r="F353" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G353" t="s">
         <v>8</v>
@@ -12361,7 +12368,7 @@
         <v>574</v>
       </c>
       <c r="I353" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.35">
@@ -12378,7 +12385,7 @@
         <v>8</v>
       </c>
       <c r="E354" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F354" t="s">
         <v>47</v>
@@ -12390,7 +12397,7 @@
         <v>574</v>
       </c>
       <c r="I354" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.35">
@@ -12407,7 +12414,7 @@
         <v>8</v>
       </c>
       <c r="E355" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F355" t="s">
         <v>47</v>
@@ -12419,7 +12426,7 @@
         <v>574</v>
       </c>
       <c r="I355" s="1" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.35">
@@ -12436,7 +12443,7 @@
         <v>8</v>
       </c>
       <c r="E356" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F356" t="s">
         <v>47</v>
@@ -12448,7 +12455,7 @@
         <v>574</v>
       </c>
       <c r="I356" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.35">
@@ -12456,7 +12463,7 @@
         <v>5</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>7</v>
@@ -12465,10 +12472,10 @@
         <v>8</v>
       </c>
       <c r="E357" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F357" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="G357" t="s">
         <v>8</v>
@@ -12477,7 +12484,7 @@
         <v>574</v>
       </c>
       <c r="I357" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.35">
@@ -12485,7 +12492,7 @@
         <v>5</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>7</v>
@@ -12494,10 +12501,10 @@
         <v>8</v>
       </c>
       <c r="E358" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F358" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="G358" t="s">
         <v>8</v>
@@ -12506,7 +12513,7 @@
         <v>574</v>
       </c>
       <c r="I358" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.35">
@@ -12514,7 +12521,7 @@
         <v>5</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>6</v>
+        <v>565</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>7</v>
@@ -12523,10 +12530,10 @@
         <v>8</v>
       </c>
       <c r="E359" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="F359" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="G359" t="s">
         <v>8</v>
@@ -12535,15 +12542,15 @@
         <v>574</v>
       </c>
       <c r="I359" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A360" s="3" t="s">
-        <v>5</v>
+        <v>534</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>565</v>
+        <v>6</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>7</v>
@@ -12564,12 +12571,12 @@
         <v>574</v>
       </c>
       <c r="I360" s="1" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A361" s="3" t="s">
-        <v>534</v>
+        <v>5</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>6</v>
@@ -12581,7 +12588,7 @@
         <v>8</v>
       </c>
       <c r="E361" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F361" t="s">
         <v>10</v>
@@ -12593,7 +12600,7 @@
         <v>574</v>
       </c>
       <c r="I361" s="1" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.35">
@@ -12610,10 +12617,10 @@
         <v>8</v>
       </c>
       <c r="E362" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F362" t="s">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G362" t="s">
         <v>8</v>
@@ -12622,7 +12629,7 @@
         <v>574</v>
       </c>
       <c r="I362" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.35">
@@ -12639,10 +12646,10 @@
         <v>8</v>
       </c>
       <c r="E363" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F363" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="G363" t="s">
         <v>8</v>
@@ -12651,7 +12658,7 @@
         <v>574</v>
       </c>
       <c r="I363" s="1" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.35">
@@ -12659,7 +12666,7 @@
         <v>5</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>6</v>
+        <v>396</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>7</v>
@@ -12668,10 +12675,10 @@
         <v>8</v>
       </c>
       <c r="E364" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F364" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="G364" t="s">
         <v>8</v>
@@ -12680,15 +12687,15 @@
         <v>574</v>
       </c>
       <c r="I364" s="1" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A365" s="3" t="s">
-        <v>5</v>
+        <v>571</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>396</v>
+        <v>6</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>7</v>
@@ -12709,57 +12716,28 @@
         <v>574</v>
       </c>
       <c r="I365" s="1" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A366" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="B366" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C366" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A366" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="B366" s="6"/>
+      <c r="C366" s="6"/>
       <c r="D366" t="s">
         <v>8</v>
       </c>
       <c r="E366" t="s">
-        <v>570</v>
+        <v>8</v>
       </c>
       <c r="F366" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="G366" t="s">
         <v>8</v>
       </c>
       <c r="H366" s="8" t="s">
-        <v>574</v>
-      </c>
-      <c r="I366" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A367" s="6" t="s">
-        <v>572</v>
-      </c>
-      <c r="B367" s="6"/>
-      <c r="C367" s="6"/>
-      <c r="D367" t="s">
-        <v>8</v>
-      </c>
-      <c r="E367" t="s">
-        <v>8</v>
-      </c>
-      <c r="F367" t="s">
-        <v>8</v>
-      </c>
-      <c r="G367" t="s">
-        <v>8</v>
-      </c>
-      <c r="H367" s="8" t="s">
         <v>8</v>
       </c>
     </row>
@@ -12768,9 +12746,13 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A367:C367"/>
+    <mergeCell ref="A366:C366"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <ignoredErrors>
+    <ignoredError sqref="H3" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>